--- a/apps/web/public/templates/Parent_Account_Import_Template.xlsx
+++ b/apps/web/public/templates/Parent_Account_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HK9\KLTN\KLTN_Project\execl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAD1ABC-53D5-4052-9BBC-E22AB4654CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC92CA06-7A5F-417B-B8AB-E42EDB6022A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="4935" windowWidth="15375" windowHeight="7785" xr2:uid="{1B6CC809-07B9-482A-8415-E567954F570C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1B6CC809-07B9-482A-8415-E567954F570C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,10 +48,13 @@
     <t>Nghề nghiệp</t>
   </si>
   <si>
-    <t>Mối quan hệ*</t>
-  </si>
-  <si>
     <t>ID sinh viên con*</t>
+  </si>
+  <si>
+    <t>Mối quan hệ*
+1. Cha
+2. Mẹ
+3. Người giám hộ</t>
   </si>
 </sst>
 </file>
@@ -116,11 +119,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,9 +457,10 @@
     <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="12" style="2" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -471,10 +483,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -489,6 +501,11 @@
       <c r="I2" s="1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{0A776D7B-21E7-4C0B-8E9C-FE3DB3554703}">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>